--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -1082,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1281,7 @@
         <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1382,7 @@
         <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>91993</v>
+        <v>91753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91753</v>
+        <v>91993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129387166</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91753</v>
+        <v>91996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>91993</v>
+        <v>91756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129387166</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91756</v>
+        <v>91998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>91762</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91762</v>
+        <v>92003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>92002</v>
+        <v>91763</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>92003</v>
+        <v>91763</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91763</v>
+        <v>92003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91763</v>
+        <v>92006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>92003</v>
+        <v>91766</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>92006</v>
+        <v>91766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91766</v>
+        <v>92006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91766</v>
+        <v>92006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>92006</v>
+        <v>91766</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129387166</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>92006</v>
+        <v>91794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91766</v>
+        <v>92034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129387166</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91794</v>
+        <v>92040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>92034</v>
+        <v>91800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129387166</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>92040</v>
+        <v>91801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91800</v>
+        <v>92041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129387166</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>91801</v>
+        <v>91806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91806</v>
+        <v>92046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>91806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>91806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B9" t="n">
-        <v>91806</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R9" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129387381</v>
       </c>
       <c r="B2" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129387135</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129387211</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>129387310</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387252</v>
+        <v>129387103</v>
       </c>
       <c r="B8" t="n">
-        <v>91806</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623701</v>
+        <v>623402</v>
       </c>
       <c r="R8" t="n">
-        <v>7026900</v>
+        <v>7026737</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129387103</v>
+        <v>129387252</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>91810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623402</v>
+        <v>623701</v>
       </c>
       <c r="R9" t="n">
-        <v>7026737</v>
+        <v>7026900</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129387381</v>
+        <v>129387252</v>
       </c>
       <c r="B2" t="n">
-        <v>91617</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -709,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623717</v>
+        <v>623701</v>
       </c>
       <c r="R2" t="n">
-        <v>7026928</v>
+        <v>7026900</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129387166</v>
+        <v>129387135</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -810,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623571</v>
+        <v>623400</v>
       </c>
       <c r="R3" t="n">
-        <v>7026735</v>
+        <v>7026739</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +880,7 @@
         <v>129387149</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129387135</v>
+        <v>129387310</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623400</v>
+        <v>623687</v>
       </c>
       <c r="R5" t="n">
-        <v>7026739</v>
+        <v>7026886</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1075,38 +1079,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129387211</v>
+        <v>129387103</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1114,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623569</v>
+        <v>623402</v>
       </c>
       <c r="R6" t="n">
-        <v>7026734</v>
+        <v>7026737</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1177,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129387310</v>
+        <v>129387166</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623687</v>
+        <v>623571</v>
       </c>
       <c r="R7" t="n">
-        <v>7026886</v>
+        <v>7026735</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1278,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129387103</v>
+        <v>129387211</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,26 +1292,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1316,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623402</v>
+        <v>623569</v>
       </c>
       <c r="R8" t="n">
-        <v>7026737</v>
+        <v>7026734</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1376,107 +1380,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>129387252</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91810</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>48</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lappticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Amylocystis lapponica</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Rävsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>623701</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7026900</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Karolina Forsén</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Karolina Forsén</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18100-2025 artfynd.xlsx
+++ b/artfynd/A 18100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387135</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387166</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,8 +1415,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129387211</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>